--- a/3. RECTIFICADOR TRIFASICO ONDA COMPLETA/datos_rect_3p_onda_completa.xlsx
+++ b/3. RECTIFICADOR TRIFASICO ONDA COMPLETA/datos_rect_3p_onda_completa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bremdows\UNSAAC\SEMESTRE X\LABORATORIO DE SISTEMAS ELECTRONICOS DE POTENCIA\lab-sistemas-electronicos-potencia\3. RECTIFICADOR TRIFASICO ONDA COMPLETA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9D5AC4B-D35F-42C2-8E8A-AE2998702EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A85DDB-28D7-4F8F-8622-8440DD6BDA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11520" yWindow="456" windowWidth="11520" windowHeight="12504" xr2:uid="{A1851927-74FE-43DE-8622-012316BDC088}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
   <si>
     <t>Vm</t>
   </si>
@@ -75,6 +75,21 @@
   </si>
   <si>
     <t>RC</t>
+  </si>
+  <si>
+    <t>Pac</t>
+  </si>
+  <si>
+    <t>Pdc</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>TUF</t>
+  </si>
+  <si>
+    <t>FP</t>
   </si>
 </sst>
 </file>
@@ -511,6 +526,13 @@
         <f>B4/F1</f>
         <v>5.8144902438649726E-2</v>
       </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6">
+        <f>B4*B6</f>
+        <v>6.6703769578509871</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -520,6 +542,13 @@
         <f>B4/B3</f>
         <v>1.0009114194337081</v>
       </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7">
+        <f>B3*B5</f>
+        <v>6.6582345382481813</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -529,40 +558,85 @@
         <f>SQRT(B7^2-1)</f>
         <v>4.2704444180907242E-2</v>
       </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8">
+        <f>E7/E6</f>
+        <v>0.99817965016377164</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9">
+        <f>E7/(3*E6)</f>
+        <v>0.33272655005459051</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10">
+        <f>E7/E6</f>
+        <v>0.99817965016377164</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>1</v>
       </c>
+      <c r="B11">
+        <v>67.2</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>2</v>
       </c>
+      <c r="B12">
+        <v>67.3</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
+      <c r="B13">
+        <f>B11/F1</f>
+        <v>3.4059807399898633E-2</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
+      <c r="B14">
+        <f>B12/F1</f>
+        <v>3.4110491637100858E-2</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>10</v>
       </c>
+      <c r="B15">
+        <f>B12/B11</f>
+        <v>1.0014880952380951</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>11</v>
+      </c>
+      <c r="B16">
+        <f>SQRT(B15^2-1)</f>
+        <v>5.4574764347891463E-2</v>
       </c>
     </row>
   </sheetData>
